--- a/协作/36-追溯矩阵.xlsx
+++ b/协作/36-追溯矩阵.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -668,13 +668,75 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>需求-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>协议改为全角色全开、零配置，并补齐本仓库 37+3 交付物</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>契约-0004</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>验收-0005</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>改动-0006</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3f1aef4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>16-代码审查报告（A-01..A-10）</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>18-专项审查报告（B-01..B-08）</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>证据-0008,证据-0009</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>已验收</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="J2:J121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="J2:J121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"passed,blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"完整,断链"</formula1>
+    <dataValidation sqref="L2:L121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"完整,断链,已验收"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
